--- a/companies/starttoscale/starttoscale-client-data-overview.xlsx
+++ b/companies/starttoscale/starttoscale-client-data-overview.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>starttoscale.nl</t>
+          <t>starttoscalefinance.com</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>8.0 KB</t>
+          <t>10.0 KB</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -1222,39 +1222,39 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>charter.json</t>
+          <t>business-cards/.DS_Store</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>13.8 KB</t>
+          <t>6.0 KB</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Brand identity spec — colors, typography, logos, images, templates</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>guidelines.md</t>
+          <t>business-cards/print/README.md</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1264,451 +1264,451 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>11.6 KB</t>
+          <t>1.3 KB</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Brand usage guidelines</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>images/16x9/i1-01-16x9.jpg</t>
+          <t>business-cards/print/c01-eu-print.pdf</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>188.1 KB</t>
+          <t>80.1 KB</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>images/16x9/i1-02-16x9.jpg</t>
+          <t>business-cards/review/business-cards.html</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>290.4 KB</t>
+          <t>5.8 KB</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>images/16x9/i1-03-16x9.jpg</t>
+          <t>business-cards/source/c01-eu-back.svg</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>137.8 KB</t>
+          <t>1.5 KB</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>images/16x9/i1-04-16x9.jpg</t>
+          <t>business-cards/source/c01-eu-front.svg</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>249.2 KB</t>
+          <t>1.3 KB</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>images/16x9/i2-01-16x9.jpg</t>
+          <t>charter.json</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>140.1 KB</t>
+          <t>13.7 KB</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Brand identity spec — colors, typography, logos, images, templates</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>images/16x9/i2-02-16x9.jpg</t>
+          <t>content/website.json</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>content</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>124.0 KB</t>
+          <t>23.1 KB</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>images/16x9/i2-03-16x9.jpg</t>
+          <t>fonts/Inter-Italic[opsz,wght].ttf</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>125.1 KB</t>
+          <t>885.3 KB</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — Inter-Italic[opsz,wght]</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>images/16x9/i2-04-16x9.jpg</t>
+          <t>fonts/Inter[opsz,wght].ttf</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>108.3 KB</t>
+          <t>856.0 KB</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — Inter[opsz,wght]</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>images/1x1/i1-01-1x1.jpg</t>
+          <t>fonts/JetBrainsMono-Bold.ttf</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>103.4 KB</t>
+          <t>112.1 KB</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — JetBrainsMono-Bold</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>images/1x1/i1-02-1x1.jpg</t>
+          <t>fonts/JetBrainsMono-OFL.txt</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>178.1 KB</t>
+          <t>4.3 KB</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — JetBrainsMono-OFL</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>images/1x1/i1-03-1x1.jpg</t>
+          <t>fonts/JetBrainsMono-Regular.ttf</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>89.9 KB</t>
+          <t>112.2 KB</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — JetBrainsMono-Regular</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>images/1x1/i1-04-1x1.jpg</t>
+          <t>fonts/Newsreader-Italic[opsz,wght].ttf</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>153.4 KB</t>
+          <t>484.1 KB</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — Newsreader-Italic[opsz,wght]</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>images/1x1/i2-01-1x1.jpg</t>
+          <t>fonts/Newsreader[opsz,wght].ttf</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>91.6 KB</t>
+          <t>441.1 KB</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — Newsreader[opsz,wght]</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>images/1x1/i2-02-1x1.jpg</t>
+          <t>fonts/OFL-Inter.txt</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>76.8 KB</t>
+          <t>4.3 KB</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — OFL-Inter</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>images/1x1/i2-03-1x1.jpg</t>
+          <t>fonts/OFL-Newsreader.txt</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>89.4 KB</t>
+          <t>4.3 KB</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — OFL-Newsreader</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>images/1x1/i2-04-1x1.jpg</t>
+          <t>guidelines.md</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Markdown</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>63.1 KB</t>
+          <t>11.6 KB</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Brand usage guidelines</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>images/2x1/i1-01-2x1.jpg</t>
+          <t>images/16x9/i1-01-16x9.jpg</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>184.2 KB</t>
+          <t>188.1 KB</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -1735,7 +1735,7 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>images/2x1/i1-02-2x1.jpg</t>
+          <t>images/16x9/i1-02-16x9.jpg</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>267.7 KB</t>
+          <t>290.4 KB</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -1762,7 +1762,7 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>images/2x1/i1-03-2x1.jpg</t>
+          <t>images/16x9/i1-03-16x9.jpg</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>125.7 KB</t>
+          <t>137.8 KB</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>images/2x1/i1-04-2x1.jpg</t>
+          <t>images/16x9/i1-04-16x9.jpg</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>223.5 KB</t>
+          <t>249.2 KB</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>images/2x1/i2-01-2x1.jpg</t>
+          <t>images/16x9/i2-01-16x9.jpg</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>128.6 KB</t>
+          <t>140.1 KB</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -1843,7 +1843,7 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>images/2x1/i2-02-2x1.jpg</t>
+          <t>images/16x9/i2-02-16x9.jpg</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>113.3 KB</t>
+          <t>124.0 KB</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -1870,7 +1870,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>images/2x1/i2-03-2x1.jpg</t>
+          <t>images/16x9/i2-03-16x9.jpg</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>110.3 KB</t>
+          <t>125.1 KB</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>images/2x1/i2-04-2x1.jpg</t>
+          <t>images/16x9/i2-04-16x9.jpg</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>100.4 KB</t>
+          <t>108.3 KB</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>images/branded/i1-01-branded.jpg</t>
+          <t>images/1x1/i1-01-1x1.jpg</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>111.7 KB</t>
+          <t>103.4 KB</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>images/branded/i1-02-branded.jpg</t>
+          <t>images/1x1/i1-02-1x1.jpg</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>170.5 KB</t>
+          <t>178.1 KB</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -1978,7 +1978,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>images/branded/i1-03-branded.jpg</t>
+          <t>images/1x1/i1-03-1x1.jpg</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>80.6 KB</t>
+          <t>89.9 KB</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -2005,7 +2005,7 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>images/branded/i1-04-branded.jpg</t>
+          <t>images/1x1/i1-04-1x1.jpg</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>133.8 KB</t>
+          <t>153.4 KB</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2032,7 +2032,7 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>images/branded/i2-01-branded.jpg</t>
+          <t>images/1x1/i2-01-1x1.jpg</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>84.2 KB</t>
+          <t>91.6 KB</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>images/branded/i2-02-branded.jpg</t>
+          <t>images/1x1/i2-02-1x1.jpg</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>64.6 KB</t>
+          <t>76.8 KB</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2086,7 +2086,7 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>images/branded/i2-03-branded.jpg</t>
+          <t>images/1x1/i2-03-1x1.jpg</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>70.5 KB</t>
+          <t>89.4 KB</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>images/branded/i2-04-branded.jpg</t>
+          <t>images/1x1/i2-04-1x1.jpg</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>53.4 KB</t>
+          <t>63.1 KB</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>images/manifest.json</t>
+          <t>images/2x1/i1-01-2x1.jpg</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>6.4 KB</t>
+          <t>184.2 KB</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -2167,7 +2167,7 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>images/source/i1-01.jpg</t>
+          <t>images/2x1/i1-02-2x1.jpg</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>427.4 KB</t>
+          <t>267.7 KB</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -2194,7 +2194,7 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>images/source/i1-02.jpg</t>
+          <t>images/2x1/i1-03-2x1.jpg</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>714.8 KB</t>
+          <t>125.7 KB</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>images/source/i1-03.jpg</t>
+          <t>images/2x1/i1-04-2x1.jpg</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>368.3 KB</t>
+          <t>223.5 KB</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -2248,7 +2248,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>images/source/i1-04.jpg</t>
+          <t>images/2x1/i2-01-2x1.jpg</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>1087.6 KB</t>
+          <t>128.6 KB</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>images/source/i2-01.jpg</t>
+          <t>images/2x1/i2-02-2x1.jpg</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>419.8 KB</t>
+          <t>113.3 KB</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -2302,7 +2302,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>images/source/i2-02.jpg</t>
+          <t>images/2x1/i2-03-2x1.jpg</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>396.1 KB</t>
+          <t>110.3 KB</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -2329,7 +2329,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>images/source/i2-03.jpg</t>
+          <t>images/2x1/i2-04-2x1.jpg</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>347.4 KB</t>
+          <t>100.4 KB</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -2356,7 +2356,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>images/source/i2-04.jpg</t>
+          <t>images/branded/i1-01-branded.jpg</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>393.7 KB</t>
+          <t>111.7 KB</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>images/text-safe/i1-01-text-safe.jpg</t>
+          <t>images/branded/i1-02-branded.jpg</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>141.3 KB</t>
+          <t>170.5 KB</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -2410,7 +2410,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>images/text-safe/i1-02-text-safe.jpg</t>
+          <t>images/branded/i1-03-branded.jpg</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>209.8 KB</t>
+          <t>80.6 KB</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -2437,7 +2437,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>images/text-safe/i1-03-text-safe.jpg</t>
+          <t>images/branded/i1-04-branded.jpg</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>102.2 KB</t>
+          <t>133.8 KB</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -2464,7 +2464,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>images/text-safe/i1-04-text-safe.jpg</t>
+          <t>images/branded/i2-01-branded.jpg</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>174.6 KB</t>
+          <t>84.2 KB</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>images/text-safe/i2-01-text-safe.jpg</t>
+          <t>images/branded/i2-02-branded.jpg</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>101.7 KB</t>
+          <t>64.6 KB</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -2518,7 +2518,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>images/text-safe/i2-02-text-safe.jpg</t>
+          <t>images/branded/i2-03-branded.jpg</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>86.8 KB</t>
+          <t>70.5 KB</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -2545,7 +2545,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>images/text-safe/i2-03-text-safe.jpg</t>
+          <t>images/branded/i2-04-branded.jpg</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>91.4 KB</t>
+          <t>53.4 KB</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>images/text-safe/i2-04-text-safe.jpg</t>
+          <t>images/manifest.json</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>73.2 KB</t>
+          <t>6.4 KB</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -2599,439 +2599,439 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>logos/apple-touch-icon-180.png</t>
+          <t>images/source/i1-01.jpg</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>2.4 KB</t>
+          <t>427.4 KB</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Logo asset — apple-touch-icon-180</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>logos/favicon-16.png</t>
+          <t>images/source/i1-02.jpg</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>0.3 KB</t>
+          <t>714.8 KB</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>Logo asset — favicon-16</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>logos/favicon-192.png</t>
+          <t>images/source/i1-03.jpg</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>2.3 KB</t>
+          <t>368.3 KB</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Logo asset — favicon-192</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>logos/favicon-32.png</t>
+          <t>images/source/i1-04.jpg</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>0.4 KB</t>
+          <t>1087.6 KB</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Logo asset — favicon-32</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>logos/favicon-512.png</t>
+          <t>images/source/i2-01.jpg</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>7.1 KB</t>
+          <t>419.8 KB</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Logo asset — favicon-512</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>logos/favicon.svg</t>
+          <t>images/source/i2-02.jpg</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>0.4 KB</t>
+          <t>396.1 KB</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>Logo asset — favicon</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>logos/icon_dark.png</t>
+          <t>images/source/i2-03.jpg</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>1.1 KB</t>
+          <t>347.4 KB</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Logo asset — icon_dark</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>logos/icon_dark.svg</t>
+          <t>images/source/i2-04.jpg</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>0.4 KB</t>
+          <t>393.7 KB</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>Logo asset — icon_dark</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>logos/logo.png</t>
+          <t>images/text-safe/i1-01-text-safe.jpg</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>9.9 KB</t>
+          <t>141.3 KB</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Logo asset — logo</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>logos/logo.svg</t>
+          <t>images/text-safe/i1-02-text-safe.jpg</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>1.0 KB</t>
+          <t>209.8 KB</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Logo asset — logo</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>logos/logo@2x.png</t>
+          <t>images/text-safe/i1-03-text-safe.jpg</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>21.2 KB</t>
+          <t>102.2 KB</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Logo asset — logo@2x</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>logos/logo@3x.png</t>
+          <t>images/text-safe/i1-04-text-safe.jpg</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>32.1 KB</t>
+          <t>174.6 KB</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>Logo asset — logo@3x</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>logos/logo_mono.svg</t>
+          <t>images/text-safe/i2-01-text-safe.jpg</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>0.9 KB</t>
+          <t>101.7 KB</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Logo asset — logo_mono</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>logos/logo_white.png</t>
+          <t>images/text-safe/i2-02-text-safe.jpg</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>7.9 KB</t>
+          <t>86.8 KB</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>Logo asset — logo_white</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>logos/logo_white.svg</t>
+          <t>images/text-safe/i2-03-text-safe.jpg</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>0.9 KB</t>
+          <t>91.4 KB</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Logo asset — logo_white</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>logos/logo_white@2x.png</t>
+          <t>images/text-safe/i2-04-text-safe.jpg</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>17.3 KB</t>
+          <t>73.2 KB</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Logo asset — logo_white@2x</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>logos/symbol.png</t>
+          <t>logos/apple-touch-icon-180.png</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
@@ -3046,19 +3046,19 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>1.2 KB</t>
+          <t>2.4 KB</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Logo asset — symbol</t>
+          <t>Logo asset — apple-touch-icon-180</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>logos/symbol.svg</t>
+          <t>logos/favicon-16.png</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -3068,24 +3068,24 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>0.6 KB</t>
+          <t>0.3 KB</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Logo asset — symbol</t>
+          <t>Logo asset — favicon-16</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>logos/symbol_white.png</t>
+          <t>logos/favicon-192.png</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -3100,19 +3100,19 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>1.1 KB</t>
+          <t>2.3 KB</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Logo asset — symbol_white</t>
+          <t>Logo asset — favicon-192</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>logos/symbol_white.svg</t>
+          <t>logos/favicon-32.png</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
@@ -3132,19 +3132,19 @@
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Logo asset — symbol_white</t>
+          <t>Logo asset — favicon-32</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/gradients/navy-amber-diag.png</t>
+          <t>logos/favicon-512.png</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -3154,51 +3154,51 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>41.5 KB</t>
+          <t>7.1 KB</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Logo asset — favicon-512</t>
         </is>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/gradients/navy-hero.png</t>
+          <t>logos/favicon.svg</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>73.0 KB</t>
+          <t>0.4 KB</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Logo asset — favicon</t>
         </is>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/gradients/navy-vignette.png</t>
+          <t>logos/icon_dark.png</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -3208,105 +3208,105 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>41.4 KB</t>
+          <t>1.1 KB</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Logo asset — icon_dark</t>
         </is>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/gradients/paper-soft.png</t>
+          <t>logos/icon_dark.svg</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>9.9 KB</t>
+          <t>0.4 KB</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Logo asset — icon_dark</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/manifest.json</t>
+          <t>logos/logo.png</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>1.1 KB</t>
+          <t>9.9 KB</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Logo asset — logo</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/motifs/corner-three-steps.png</t>
+          <t>logos/logo.svg</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>10.3 KB</t>
+          <t>1.0 KB</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Logo asset — logo</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/motifs/pattern-full-navy.png</t>
+          <t>logos/logo@2x.png</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -3316,24 +3316,24 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>27.7 KB</t>
+          <t>21.2 KB</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Logo asset — logo@2x</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/motifs/pattern-full-paper.png</t>
+          <t>logos/logo@3x.png</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -3343,235 +3343,235 @@
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>27.6 KB</t>
+          <t>32.1 KB</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Logo asset — logo@3x</t>
         </is>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-01-bw-amber.jpg</t>
+          <t>logos/logo_mono.svg</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>164.3 KB</t>
+          <t>0.9 KB</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — logo_mono</t>
         </is>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-01-navy35.jpg</t>
+          <t>logos/logo_white.png</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>152.1 KB</t>
+          <t>7.9 KB</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — logo_white</t>
         </is>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-01-navy55.jpg</t>
+          <t>logos/logo_white.svg</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>111.7 KB</t>
+          <t>0.9 KB</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — logo_white</t>
         </is>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-02-bw-amber.jpg</t>
+          <t>logos/logo_white@2x.png</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>227.1 KB</t>
+          <t>17.3 KB</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — logo_white@2x</t>
         </is>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-02-navy35.jpg</t>
+          <t>logos/symbol.png</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>227.9 KB</t>
+          <t>1.2 KB</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — symbol</t>
         </is>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-02-navy55.jpg</t>
+          <t>logos/symbol.svg</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>170.5 KB</t>
+          <t>0.6 KB</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — symbol</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-03-navy35.jpg</t>
+          <t>logos/symbol_white.png</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>110.2 KB</t>
+          <t>1.1 KB</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — symbol_white</t>
         </is>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-03-navy55.jpg</t>
+          <t>logos/symbol_white.svg</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>80.6 KB</t>
+          <t>0.4 KB</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — symbol_white</t>
         </is>
       </c>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-04-bw-amber.jpg</t>
+          <t>pptx-assets/gradients/navy-amber-diag.png</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
@@ -3581,24 +3581,24 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>209.1 KB</t>
+          <t>41.5 KB</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-04-navy35.jpg</t>
+          <t>pptx-assets/gradients/navy-hero.png</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -3608,24 +3608,24 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>193.5 KB</t>
+          <t>73.0 KB</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
         </is>
       </c>
     </row>
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i1-04-navy55.jpg</t>
+          <t>pptx-assets/gradients/navy-vignette.png</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
@@ -3635,24 +3635,24 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>133.8 KB</t>
+          <t>41.4 KB</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
         </is>
       </c>
     </row>
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i2-01-navy35.jpg</t>
+          <t>pptx-assets/gradients/paper-soft.png</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -3662,24 +3662,24 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>110.7 KB</t>
+          <t>9.9 KB</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
         </is>
       </c>
     </row>
     <row r="109" ht="16" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i2-01-navy55.jpg</t>
+          <t>pptx-assets/manifest.json</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
@@ -3689,24 +3689,24 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>84.2 KB</t>
+          <t>1.1 KB</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
         </is>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i2-02-navy35.jpg</t>
+          <t>pptx-assets/motifs/corner-three-steps.png</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>96.1 KB</t>
+          <t>10.3 KB</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
         </is>
       </c>
     </row>
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i2-02-navy55.jpg</t>
+          <t>pptx-assets/motifs/pattern-full-navy.png</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
@@ -3743,24 +3743,24 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>64.6 KB</t>
+          <t>27.7 KB</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
         </is>
       </c>
     </row>
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i2-03-navy35.jpg</t>
+          <t>pptx-assets/motifs/pattern-full-paper.png</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -3770,24 +3770,24 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>99.7 KB</t>
+          <t>27.6 KB</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
         </is>
       </c>
     </row>
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i2-03-navy55.jpg</t>
+          <t>pptx-assets/overlays/i1-01-bw-amber.jpg</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>70.5 KB</t>
+          <t>164.3 KB</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i2-04-navy35.jpg</t>
+          <t>pptx-assets/overlays/i1-01-navy35.jpg</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>84.2 KB</t>
+          <t>152.1 KB</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
@@ -3841,7 +3841,7 @@
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/i2-04-navy55.jpg</t>
+          <t>pptx-assets/overlays/i1-01-navy55.jpg</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>53.4 KB</t>
+          <t>111.7 KB</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
@@ -3868,303 +3868,735 @@
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>profile.json</t>
+          <t>pptx-assets/overlays/i1-02-bw-amber.jpg</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>pptx-assets</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>5.6 KB</t>
+          <t>227.1 KB</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>Company profile — description, services, legal identity</t>
+          <t>Pre-composited overlay image for PowerPoint</t>
         </is>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>templates/docx/letterhead.docx</t>
+          <t>pptx-assets/overlays/i1-02-navy35.jpg</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>pptx-assets</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>DOCX</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>32.6 KB</t>
+          <t>227.9 KB</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>Branded Word styles template</t>
+          <t>Pre-composited overlay image for PowerPoint</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>templates/docx/styles.docx</t>
+          <t>pptx-assets/overlays/i1-02-navy55.jpg</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>pptx-assets</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>DOCX</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>10.8 KB</t>
+          <t>170.5 KB</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>Branded Word styles template</t>
+          <t>Pre-composited overlay image for PowerPoint</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>templates/html/business-cards.html</t>
+          <t>pptx-assets/overlays/i1-03-navy35.jpg</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>pptx-assets</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>5.8 KB</t>
+          <t>110.2 KB</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>Branded HTML template</t>
+          <t>Pre-composited overlay image for PowerPoint</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>templates/html/email-signature.html</t>
+          <t>pptx-assets/overlays/i1-03-navy55.jpg</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>pptx-assets</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>7.0 KB</t>
+          <t>80.6 KB</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>Branded HTML template</t>
+          <t>Pre-composited overlay image for PowerPoint</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>templates/pptx/closing.html</t>
+          <t>pptx-assets/overlays/i1-04-bw-amber.jpg</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>pptx-assets</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>2.6 KB</t>
+          <t>209.1 KB</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>HTML template for PowerPoint slide layout</t>
+          <t>Pre-composited overlay image for PowerPoint</t>
         </is>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>templates/pptx/content.html</t>
+          <t>pptx-assets/overlays/i1-04-navy35.jpg</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>pptx-assets</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>2.6 KB</t>
+          <t>193.5 KB</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>HTML template for PowerPoint slide layout</t>
+          <t>Pre-composited overlay image for PowerPoint</t>
         </is>
       </c>
     </row>
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>templates/pptx/cover.html</t>
+          <t>pptx-assets/overlays/i1-04-navy55.jpg</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>pptx-assets</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>3.2 KB</t>
+          <t>133.8 KB</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>HTML template for PowerPoint slide layout</t>
+          <t>Pre-composited overlay image for PowerPoint</t>
         </is>
       </c>
     </row>
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>templates/pptx/footer-bar.html</t>
+          <t>pptx-assets/overlays/i2-01-navy35.jpg</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>pptx-assets</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>1.2 KB</t>
+          <t>110.7 KB</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>HTML template for PowerPoint slide layout</t>
+          <t>Pre-composited overlay image for PowerPoint</t>
         </is>
       </c>
     </row>
     <row r="125" ht="16" customHeight="1">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>templates/pptx/section-divider.html</t>
+          <t>pptx-assets/overlays/i2-01-navy55.jpg</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>pptx-assets</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>1.9 KB</t>
+          <t>84.2 KB</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>HTML template for PowerPoint slide layout</t>
+          <t>Pre-composited overlay image for PowerPoint</t>
         </is>
       </c>
     </row>
     <row r="126" ht="16" customHeight="1">
       <c r="A126" s="10" t="inlineStr">
         <is>
+          <t>pptx-assets/overlays/i2-02-navy35.jpg</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>96.1 KB</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/i2-02-navy55.jpg</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>64.6 KB</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/i2-03-navy35.jpg</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>99.7 KB</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/i2-03-navy55.jpg</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>70.5 KB</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/i2-04-navy35.jpg</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>84.2 KB</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/i2-04-navy55.jpg</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>53.4 KB</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>profile.json</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="inlineStr">
+        <is>
+          <t>9.0 KB</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>Company profile — description, services, legal identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>starttoscale-client-data-overview.xlsx</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>XLSX</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>15.8 KB</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="16" customHeight="1">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>templates/docx/letterhead.docx</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>DOCX</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>32.6 KB</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>Branded Word styles template</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="16" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>templates/docx/styles.docx</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>DOCX</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>10.8 KB</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>Branded Word styles template</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>templates/html/email-signature.html</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>7.0 KB</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>Branded HTML template</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>templates/pptx/closing.html</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>2.6 KB</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>HTML template for PowerPoint slide layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>templates/pptx/content.html</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>2.6 KB</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>HTML template for PowerPoint slide layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>templates/pptx/cover.html</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>3.2 KB</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>HTML template for PowerPoint slide layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>templates/pptx/footer-bar.html</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>1.2 KB</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>HTML template for PowerPoint slide layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>templates/pptx/section-divider.html</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>1.9 KB</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>HTML template for PowerPoint slide layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
           <t>tokens.css</t>
         </is>
       </c>
-      <c r="B126" s="10" t="inlineStr">
+      <c r="B142" s="10" t="inlineStr">
         <is>
           <t>root</t>
         </is>
       </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>CSS</t>
         </is>
       </c>
-      <c r="D126" s="10" t="inlineStr">
+      <c r="D142" s="10" t="inlineStr">
         <is>
           <t>11.3 KB</t>
         </is>
       </c>
-      <c r="E126" s="11" t="inlineStr">
+      <c r="E142" s="11" t="inlineStr">
         <is>
           <t>CSS design tokens mapping brand colors to CSS variables</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="8" customHeight="1"/>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
+    <row r="143" ht="8" customHeight="1"/>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
         <is>
           <t>Start to Scale Financial Management  ·  Confidential — Not for distribution</t>
         </is>
@@ -4172,8 +4604,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A144:F144"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A128:F128"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5303,7 +5735,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>wilgert@starttoscale.nl</t>
+          <t>wilgert@starttoscalefinance.nl</t>
         </is>
       </c>
     </row>
